--- a/assets/constructions/examples/ctd_mih_threadmill.xlsx
+++ b/assets/constructions/examples/ctd_mih_threadmill.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,11 +659,31 @@
           <t>zefp</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TM4SC-D42-M16-3U</t>
+          <t>TM4SC-D31-M12-2U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -686,19 +706,19 @@
         <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>0.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
         <v>4</v>
@@ -731,25 +751,25 @@
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="W2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>34</v>
+        <v>28.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>34</v>
+        <v>28.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
@@ -777,7 +797,7 @@
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M16</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -786,7 +806,7 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -798,12 +818,26 @@
       </c>
       <c r="AT2" t="n">
         <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>390.46</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>34314.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TM1SC-D17-M08-2U</t>
+          <t>TM1SC-D15-M06-2U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -826,19 +860,19 @@
         <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
         <v>0.5</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
         <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -871,25 +905,25 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>16.75</v>
+        <v>14.75</v>
       </c>
       <c r="W3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>10.6</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="n">
-        <v>22.4</v>
+        <v>20.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>22.4</v>
+        <v>20.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
@@ -917,7 +951,7 @@
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M8</t>
+          <t>METRIC_THREAD:M6</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -926,7 +960,7 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -938,12 +972,26 @@
       </c>
       <c r="AT3" t="n">
         <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>223.61</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>19651.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TM3SC-D36-M16-3U</t>
+          <t>TM4SC-D42-M16-3U</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -966,22 +1014,22 @@
         <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>0.5</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -1005,13 +1053,13 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>36.5</v>
+        <v>42</v>
       </c>
       <c r="W4" t="n">
         <v>16</v>
@@ -1023,10 +1071,10 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD4" t="n">
         <v>55</v>
@@ -1077,13 +1125,27 @@
         </is>
       </c>
       <c r="AT4" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>435.61</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>38282.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TM1SC-D15-M06-2U</t>
+          <t>TM2SC-D23-M10-2U</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1106,7 +1168,7 @@
         <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>0.5</v>
@@ -1121,7 +1183,7 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1145,31 +1207,31 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.75</v>
+        <v>22.65</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X5" t="n">
-        <v>10.6</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>20.4</v>
+        <v>19.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.4</v>
+        <v>19.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
@@ -1197,7 +1259,7 @@
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M6</t>
+          <t>METRIC_THREAD:M10</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1206,7 +1268,7 @@
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1217,13 +1279,27 @@
         </is>
       </c>
       <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
         <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>259.19</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>22778.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TM2SC-D23-M10-2U</t>
+          <t>TM3SC-D26-M12-2U</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1252,16 +1328,16 @@
         <v>0.5</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1285,31 +1361,31 @@
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V6" t="n">
-        <v>22.65</v>
+        <v>26.6</v>
       </c>
       <c r="W6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="n">
-        <v>19.4</v>
+        <v>25.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>19.4</v>
+        <v>25.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
@@ -1337,7 +1413,7 @@
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>METRIC_THREAD:M10</t>
+          <t>METRIC_THREAD:M12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1346,7 +1422,7 @@
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -1357,7 +1433,21 @@
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>25529.9</v>
       </c>
     </row>
   </sheetData>
